--- a/artfynd/A 15571-2024 artfynd.xlsx
+++ b/artfynd/A 15571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83826640</v>
+        <v>13826357</v>
       </c>
       <c r="B2" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2779</v>
+        <v>106670</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>sållning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Guldlockmossa (Skyddsvärt träd), Sk</t>
+          <t>Börringekloster, i parken, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393665.70017752</v>
+        <v>393978</v>
       </c>
       <c r="R2" t="n">
-        <v>6152306.466187214</v>
+        <v>6152584</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,33 +743,18 @@
           <t>Börringe</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1AD2C510-ECBD-4180-8710-9BE1D82C9D41</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-09-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1925-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1925-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -780,144 +762,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Alkärr.</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Göteborgs naturhistoriska museum (GNM)</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>GNM-MF-71642</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Levenskog</t>
+          <t>Jan Edelsjö</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Levenskog</t>
+          <t>Hans Lohmander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>83826639</v>
-      </c>
-      <c r="B3" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>655</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Oxtungssvamp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Fistulina hepatica</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Oxtungssvamp (Skyddsvärt träd), Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>393665.7550308957</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6152308.730523511</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Svedala</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Börringe</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>04B4C278-37BF-46D3-BEB4-487ADA60F6C8</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2007-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2007-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Per Levenskog</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Per Levenskog</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
+          <t>Markfaunaregistret GNM</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15571-2024 artfynd.xlsx
+++ b/artfynd/A 15571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,8 +798,16 @@
           <t>Markfaunaregistret GNM</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13826357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>